--- a/legisq-admin/static/dataset/bills.xlsx
+++ b/legisq-admin/static/dataset/bills.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>bill_no</t>
   </si>
@@ -46,7 +46,10 @@
     <t>Rajya Sabha</t>
   </si>
   <si>
-    <t>Apple Vision Pro</t>
+    <t>Repeat Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRUGS </t>
   </si>
 </sst>
 </file>
@@ -386,6 +389,23 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45709.0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
